--- a/output/roomself_excel/11196.xlsx
+++ b/output/roomself_excel/11196.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>392757</v>
+        <v>113157</v>
       </c>
       <c r="D2" t="n">
-        <v>6392</v>
+        <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>1184</v>
+        <v>314</v>
       </c>
       <c r="F2" t="n">
-        <v>425</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>126360</v>
+        <v>245670</v>
       </c>
       <c r="D3" t="n">
-        <v>2868</v>
+        <v>4096</v>
       </c>
       <c r="E3" t="n">
-        <v>312</v>
+        <v>668</v>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64170</v>
+        <v>126360</v>
       </c>
       <c r="D4" t="n">
-        <v>2244</v>
+        <v>2868</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>41249</v>
+        <v>90100</v>
       </c>
       <c r="D5" t="n">
-        <v>1656</v>
+        <v>2420</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -554,14 +554,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24490</v>
+        <v>41249</v>
       </c>
       <c r="D6" t="n">
-        <v>1252</v>
+        <v>1656</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -576,17 +576,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>90100</v>
+        <v>33930</v>
       </c>
       <c r="D7" t="n">
-        <v>2420</v>
+        <v>1504</v>
       </c>
       <c r="E7" t="n">
-        <v>146</v>
+        <v>210</v>
       </c>
       <c r="F7" t="n">
         <v>35</v>
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21684</v>
+        <v>64170</v>
       </c>
       <c r="D8" t="n">
-        <v>1180</v>
+        <v>2244</v>
       </c>
       <c r="E8" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -624,15 +624,59 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>24490</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1252</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>21684</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1180</v>
+      </c>
+      <c r="E10" t="n">
+        <v>191</v>
+      </c>
+      <c r="F10" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>41474</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>1644</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>224</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>21</v>
       </c>
     </row>

--- a/output/roomself_excel/11196.xlsx
+++ b/output/roomself_excel/11196.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,23 @@
       <c r="D2" t="n">
         <v>2700</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>314</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>35</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +543,31 @@
       <c r="D3" t="n">
         <v>4096</v>
       </c>
-      <c r="E3" t="n">
-        <v>668</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>425</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="G3" t="n">
+        <v>34</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>634</v>
+      </c>
+      <c r="J3" t="n">
+        <v>35</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +584,31 @@
       <c r="D4" t="n">
         <v>2868</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>312</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>34</v>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>405</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +625,31 @@
       <c r="D5" t="n">
         <v>2420</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>265</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>146</v>
       </c>
-      <c r="F5" t="n">
+      <c r="J5" t="n">
         <v>35</v>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +666,15 @@
       <c r="D6" t="n">
         <v>1656</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +691,23 @@
       <c r="D7" t="n">
         <v>1504</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>210</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>35</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +724,31 @@
       <c r="D8" t="n">
         <v>2244</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="G8" t="n">
+        <v>11</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>195</v>
+      </c>
+      <c r="J8" t="n">
+        <v>17</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +765,23 @@
       <c r="D9" t="n">
         <v>1252</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="G9" t="n">
+        <v>17</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +798,31 @@
       <c r="D10" t="n">
         <v>1180</v>
       </c>
-      <c r="E10" t="n">
-        <v>191</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>174</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="G10" t="n">
+        <v>35</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>139</v>
+      </c>
+      <c r="J10" t="n">
+        <v>35</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,10 +839,37 @@
       <c r="D11" t="n">
         <v>1644</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>233</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>224</v>
       </c>
-      <c r="F11" t="n">
+      <c r="J11" t="n">
+        <v>21</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>178</v>
+      </c>
+      <c r="M11" t="n">
         <v>21</v>
       </c>
     </row>
